--- a/python_in_excel_latest_record_by_group_demo.xlsx
+++ b/python_in_excel_latest_record_by_group_demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE12F93B-E7D7-4BF7-B508-51F1F460F184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE99AFE-DDDF-44BC-AF57-32A1B956132A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Activity" sheetId="1" r:id="rId1"/>
@@ -48,11 +48,81 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="14">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="11"/>
+          <xlrd:rvb i="12"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="13"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="14"/>
         </ext>
       </extLst>
     </bk>
@@ -66,31 +136,24 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
+          <xlrd:rvb i="6"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
+          <xlrd:rvb i="15"/>
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="14">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -105,6 +168,33 @@
     </bk>
     <bk>
       <rc t="2" v="4"/>
+    </bk>
+    <bk>
+      <rc t="2" v="5"/>
+    </bk>
+    <bk>
+      <rc t="2" v="6"/>
+    </bk>
+    <bk>
+      <rc t="2" v="7"/>
+    </bk>
+    <bk>
+      <rc t="2" v="8"/>
+    </bk>
+    <bk>
+      <rc t="2" v="9"/>
+    </bk>
+    <bk>
+      <rc t="2" v="10"/>
+    </bk>
+    <bk>
+      <rc t="2" v="11"/>
+    </bk>
+    <bk>
+      <rc t="2" v="12"/>
+    </bk>
+    <bk>
+      <rc t="2" v="13"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -113,7 +203,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization>
+    <initialization userModified="1">
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -134,7 +224,7 @@
 df</code>
     </pythonScript>
     <pythonScript>
-      <code>latest_activity = df.loc[ df.groupby("customer")["activity_date"].idxmax()] 
+      <code>latest_activity = df.loc[df.groupby("customer")["activity_date"].idxmax()] 
 latest_activity</code>
     </pythonScript>
     <pythonScript>
@@ -146,7 +236,12 @@
 latest_activity</code>
     </pythonScript>
     <pythonScript>
-      <code>latest_activity = (df.sort_values( ["activity_date", "activity_id"], ascending=[False, False] ) .drop_duplicates("customer").reset_index(drop=True))
+      <code>df["activity_date"] = pd.to_datetime( df["activity_date"], errors="coerce") 
+df = df.dropna(subset=["activity_date"])
+df</code>
+    </pythonScript>
+    <pythonScript>
+      <code>latest_activity = (df.sort_values( ["activity_date", "activity_id"], ascending=[False, False]).drop_duplicates("customer") )
 latest_activity</code>
     </pythonScript>
   </pythonScripts>
@@ -154,7 +249,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="12">
   <si>
     <t>customer</t>
   </si>
@@ -185,14 +280,17 @@
   <si>
     <t>Renewal</t>
   </si>
+  <si>
+    <t>Cedar Group</t>
+  </si>
+  <si>
+    <t>Onboarding call</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\$#,##0"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -201,21 +299,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -232,11 +324,15 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -296,7 +392,7 @@
 
 <file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
 <arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
-  <a r="10" c="5">
+  <a r="12" c="5">
     <v t="s"/>
     <v t="s">customer</v>
     <v t="s">activity_date</v>
@@ -313,38 +409,48 @@
     <v t="s">Purchase</v>
     <v>750</v>
     <v>2</v>
+    <v t="s">Cedar Group</v>
+    <v t="r">2</v>
+    <v t="s">Onboarding call</v>
+    <v>0</v>
+    <v>3</v>
     <v t="s">Acme Co</v>
-    <v t="r">2</v>
+    <v t="r">3</v>
     <v t="s">Support call</v>
     <v>0</v>
-    <v>3</v>
+    <v>4</v>
     <v t="s">Delta Inc</v>
-    <v t="r">3</v>
+    <v t="r">4</v>
     <v t="s">Purchase</v>
     <v>2100</v>
-    <v>4</v>
-    <v t="s">Bravo LLC</v>
-    <v t="r">4</v>
-    <v t="s">Renewal</v>
-    <v>900</v>
-    <v>5</v>
-    <v t="s">Acme Co</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v>7</v>
+    <v t="s">Cedar Group</v>
     <v t="r">5</v>
     <v t="s">Purchase</v>
-    <v>1450</v>
-    <v>6</v>
+    <v>1850</v>
+    <v>8</v>
     <v t="s">Delta Inc</v>
     <v t="r">6</v>
     <v t="s">Support call</v>
     <v>0</v>
-    <v>7</v>
+    <v>9</v>
     <v t="s">Bravo LLC</v>
     <v t="r">7</v>
     <v t="s">Purchase</v>
     <v>1100</v>
-    <v>8</v>
+    <v>10</v>
+    <v t="s">Cedar Group</v>
+    <v t="r">8</v>
+    <v t="s">Renewal</v>
+    <v>1950</v>
+    <v>11</v>
     <v t="s">Delta Inc</v>
-    <v t="r">8</v>
+    <v t="r">9</v>
     <v t="s">Renewal</v>
     <v>2200</v>
   </a>
@@ -352,7 +458,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="16">
   <rv s="0">
     <fb>46027</fb>
     <v>2</v>
@@ -362,6 +468,10 @@
     <v>2</v>
   </rv>
   <rv s="0">
+    <fb>46044</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
     <fb>46067</fb>
     <v>2</v>
   </rv>
@@ -370,47 +480,54 @@
     <v>2</v>
   </rv>
   <rv s="0">
-    <fb>46084</fb>
+    <fb>46106</fb>
     <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46114</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46127</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46140</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>46148</fb>
+    <v>2</v>
+  </rv>
+  <rv s="1">
+    <v>0</v>
+  </rv>
+  <rv s="2">
+    <v>DataFrame</v>
+    <v>1</v>
+    <v>10</v>
+  </rv>
+  <rv s="3">
+    <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
+    <v>DataFrame</v>
+    <v xml:space="preserve">       customer activity_date    activity_type  amount
+0       Acme Co    2026-01-05         Purchase    1200
+1     Bravo LLC    2026-01-08         Purchase     750
+2   Cedar Group    2026-01-22  Onboarding call       0
+3       Acme Co    2026-02-14   ...</v>
+    <v>11</v>
+    <v>3</v>
   </rv>
   <rv s="0">
     <fb>46099</fb>
     <v>2</v>
   </rv>
   <rv s="0">
-    <fb>46114</fb>
+    <fb>46084</fb>
     <v>2</v>
   </rv>
-  <rv s="0">
-    <fb>46127</fb>
-    <v>2</v>
-  </rv>
-  <rv s="0">
-    <fb>46148</fb>
-    <v>2</v>
-  </rv>
-  <rv s="1">
-    <v>0</v>
-  </rv>
-  <rv s="2">
-    <v>DataFrame</v>
-    <v>1</v>
-    <v>9</v>
-  </rv>
-  <rv s="3">
-    <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
-    <v>DataFrame</v>
-    <v xml:space="preserve">    customer activity_date activity_type  amount
-0    Acme Co    2026-01-05      Purchase    1200
-1  Bravo LLC    2026-01-08      Purchase     750
-2    Acme Co    2026-02-14  Support call       0
-3  Delta Inc    2026-02-20      Purchase    2100
-4  Brav...</v>
-    <v>10</v>
-    <v>3</v>
-  </rv>
   <rv s="4">
-    <v>0c3a3dd57caa4223bd8eaad24fff82f9</v>
+    <v>a30953fccdf3492c86c6b3983acb0e27</v>
     <v>'activity_id'</v>
     <v>KeyError</v>
     <v>18</v>
@@ -453,7 +570,7 @@
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbData count="4">
     <spb s="0">
-      <v>9</v>
+      <v>12</v>
       <v>4</v>
       <v>DataFrame</v>
       <v>arrayPreview</v>
@@ -511,7 +628,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="customer_activity" displayName="customer_activity" ref="A1:D10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="customer_activity" displayName="customer_activity" ref="A1:D13">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="customer"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="activity_date"/>
@@ -671,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="13.7"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -695,128 +812,170 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>46027</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>1200</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>46030</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>750</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46044</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B5" s="3">
         <v>46067</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B6" s="3">
         <v>46073</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D6" s="2">
         <v>2100</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B7" s="3">
         <v>46084</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D7" s="2">
         <v>900</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B8" s="3">
         <v>46099</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D8" s="2">
         <v>1450</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46106</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B10" s="3">
         <v>46114</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D10" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B11" s="3">
         <v>46127</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D11" s="2">
         <v>1100</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B13" s="3">
         <v>46148</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D13" s="2">
         <v>2200</v>
       </c>
     </row>
@@ -830,7 +989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B112E3F-C70A-4A17-B0A2-871E528F097B}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="13.7"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
@@ -846,7 +1005,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="str" cm="1">
-        <f t="array" ref="A3:E6">_xlfn._xlws.PY(1,0)</f>
+        <f t="array" ref="A3:E7">_xlfn._xlws.PY(1,0)</f>
         <v/>
       </c>
       <c r="B3" t="str">
@@ -864,7 +1023,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="str">
         <v>Acme Co</v>
@@ -881,7 +1040,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="str">
         <v>Bravo LLC</v>
@@ -898,138 +1057,366 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="str">
-        <v>Delta Inc</v>
+        <v>Cedar Group</v>
       </c>
       <c r="C6" vm="4">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="D6" t="str">
         <v>Renewal</v>
       </c>
       <c r="E6">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>11</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Delta Inc</v>
+      </c>
+      <c r="C7" vm="5">
+        <v>46148</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Renewal</v>
+      </c>
+      <c r="E7">
         <v>2200</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="str" cm="1">
-        <f t="array" ref="A8:D11">_xlfn._xlws.PY(2,0)</f>
+    <row r="9" spans="1:5">
+      <c r="A9" t="str" cm="1">
+        <f t="array" ref="A9:D13">_xlfn._xlws.PY(2,0)</f>
         <v>customer</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B9" t="str">
         <v>activity_date</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C9" t="str">
         <v>activity_type</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D9" t="str">
         <v>amount</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="str">
-        <v>Acme Co</v>
-      </c>
-      <c r="B9" vm="2">
-        <v>46099</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Purchase</v>
-      </c>
-      <c r="D9">
-        <v>1450</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="str">
-        <v>Bravo LLC</v>
-      </c>
-      <c r="B10" vm="3">
-        <v>46127</v>
+        <v>Acme Co</v>
+      </c>
+      <c r="B10" vm="2">
+        <v>46099</v>
       </c>
       <c r="C10" t="str">
         <v>Purchase</v>
       </c>
       <c r="D10">
-        <v>1100</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="str">
+        <v>Bravo LLC</v>
+      </c>
+      <c r="B11" vm="3">
+        <v>46127</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Purchase</v>
+      </c>
+      <c r="D11">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="str">
+        <v>Cedar Group</v>
+      </c>
+      <c r="B12" vm="4">
+        <v>46140</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Renewal</v>
+      </c>
+      <c r="D12">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="str">
         <v>Delta Inc</v>
       </c>
-      <c r="B11" vm="4">
+      <c r="B13" vm="5">
         <v>46148</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C13" t="str">
         <v>Renewal</v>
       </c>
-      <c r="D11">
+      <c r="D13">
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="str" cm="1">
-        <f t="array" ref="A13:D16">_xlfn._xlws.PY(3,0)</f>
+    <row r="15" spans="1:5">
+      <c r="A15" t="str" cm="1">
+        <f t="array" ref="A15:D19">_xlfn._xlws.PY(3,0)</f>
         <v>customer</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B15" t="str">
         <v>activity_date</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C15" t="str">
         <v>activity_type</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D15" t="str">
         <v>amount</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="str">
-        <v>Delta Inc</v>
-      </c>
-      <c r="B14" vm="4">
-        <v>46148</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Renewal</v>
-      </c>
-      <c r="D14">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="str">
-        <v>Bravo LLC</v>
-      </c>
-      <c r="B15" vm="3">
-        <v>46127</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Purchase</v>
-      </c>
-      <c r="D15">
-        <v>1100</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="str">
+        <v>Delta Inc</v>
+      </c>
+      <c r="B16" vm="5">
+        <v>46148</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Renewal</v>
+      </c>
+      <c r="D16">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="str">
+        <v>Cedar Group</v>
+      </c>
+      <c r="B17" vm="4">
+        <v>46140</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Renewal</v>
+      </c>
+      <c r="D17">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="str">
+        <v>Bravo LLC</v>
+      </c>
+      <c r="B18" vm="3">
+        <v>46127</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Purchase</v>
+      </c>
+      <c r="D18">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="str">
         <v>Acme Co</v>
       </c>
-      <c r="B16" vm="2">
+      <c r="B19" vm="2">
         <v>46099</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C19" t="str">
         <v>Purchase</v>
       </c>
-      <c r="D16">
+      <c r="D19">
         <v>1450</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="e" cm="1" vm="5">
-        <f t="array" ref="A18">_xlfn._xlws.PY(4,1)</f>
+    <row r="21" spans="1:4">
+      <c r="A21" t="str" cm="1">
+        <f t="array" ref="A21:D33">_xlfn._xlws.PY(4,0)</f>
+        <v>customer</v>
+      </c>
+      <c r="B21" t="str">
+        <v>activity_date</v>
+      </c>
+      <c r="C21" t="str">
+        <v>activity_type</v>
+      </c>
+      <c r="D21" t="str">
+        <v>amount</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="str">
+        <v>Acme Co</v>
+      </c>
+      <c r="B22" vm="6">
+        <v>46027</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Purchase</v>
+      </c>
+      <c r="D22">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="str">
+        <v>Bravo LLC</v>
+      </c>
+      <c r="B23" vm="7">
+        <v>46030</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Purchase</v>
+      </c>
+      <c r="D23">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="str">
+        <v>Cedar Group</v>
+      </c>
+      <c r="B24" vm="8">
+        <v>46044</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Onboarding call</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="str">
+        <v>Acme Co</v>
+      </c>
+      <c r="B25" vm="9">
+        <v>46067</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Support call</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="str">
+        <v>Delta Inc</v>
+      </c>
+      <c r="B26" vm="10">
+        <v>46073</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Purchase</v>
+      </c>
+      <c r="D26">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="str">
+        <v>Bravo LLC</v>
+      </c>
+      <c r="B27" vm="11">
+        <v>46084</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Renewal</v>
+      </c>
+      <c r="D27">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="str">
+        <v>Acme Co</v>
+      </c>
+      <c r="B28" vm="2">
+        <v>46099</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Purchase</v>
+      </c>
+      <c r="D28">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="str">
+        <v>Cedar Group</v>
+      </c>
+      <c r="B29" vm="12">
+        <v>46106</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Purchase</v>
+      </c>
+      <c r="D29">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="str">
+        <v>Delta Inc</v>
+      </c>
+      <c r="B30" vm="13">
+        <v>46114</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Support call</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="str">
+        <v>Bravo LLC</v>
+      </c>
+      <c r="B31" vm="3">
+        <v>46127</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Purchase</v>
+      </c>
+      <c r="D31">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="str">
+        <v>Cedar Group</v>
+      </c>
+      <c r="B32" vm="4">
+        <v>46140</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Renewal</v>
+      </c>
+      <c r="D32">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="str">
+        <v>Delta Inc</v>
+      </c>
+      <c r="B33" vm="5">
+        <v>46148</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Renewal</v>
+      </c>
+      <c r="D33">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="e" cm="1" vm="14">
+        <f t="array" ref="A36">_xlfn._xlws.PY(5,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
